--- a/Hand_edited_log/1/student/cuongnvhe181200/TC6/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/cuongnvhe181200/TC6/GradeDetail.xlsx
@@ -1104,10 +1104,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>62924</x:v>
+        <x:v>51765</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>48</x:v>
@@ -1160,10 +1160,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>62924</x:v>
+        <x:v>51765</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,10 +1216,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>62924</x:v>
+        <x:v>51765</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>48</x:v>
@@ -1272,10 +1272,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>62924</x:v>
+        <x:v>51765</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>48</x:v>
@@ -1328,10 +1328,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>62924</x:v>
+        <x:v>51765</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>58</x:v>
@@ -1440,10 +1440,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>62924</x:v>
+        <x:v>51765</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1496,10 +1496,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>62924</x:v>
+        <x:v>51765</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1552,10 +1552,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>62924</x:v>
+        <x:v>51765</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,10 +1608,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>62924</x:v>
+        <x:v>51765</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>58</x:v>
@@ -1720,10 +1720,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>62927</x:v>
+        <x:v>51776</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>48</x:v>
@@ -1776,10 +1776,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>62927</x:v>
+        <x:v>51776</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,10 +1832,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>62927</x:v>
+        <x:v>51776</x:v>
       </x:c>
       <x:c r="Q15" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
         <x:v>48</x:v>
@@ -1888,10 +1888,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>62927</x:v>
+        <x:v>51776</x:v>
       </x:c>
       <x:c r="Q16" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
         <x:v>48</x:v>
@@ -1944,10 +1944,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>62927</x:v>
+        <x:v>51776</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R17" s="3" t="s">
         <x:v>58</x:v>
@@ -2056,10 +2056,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>62927</x:v>
+        <x:v>51776</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2112,10 +2112,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>62927</x:v>
+        <x:v>51776</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2168,10 +2168,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>62927</x:v>
+        <x:v>51776</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,10 +2224,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>62927</x:v>
+        <x:v>51776</x:v>
       </x:c>
       <x:c r="Q22" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R22" s="3" t="s">
         <x:v>58</x:v>
